--- a/partner_results/ncit/ClassMissingCreationDate_ncit.xlsx
+++ b/partner_results/ncit/ClassMissingCreationDate_ncit.xlsx
@@ -465,18 +465,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>count [ncit]</t>
+          <t>colorimetry [ncit]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Determining the number or amount of something.</t>
+          <t>An assessment used to quantify and describe the colors within the visible spectrum of light.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -503,18 +503,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>colorimetry [ncit]</t>
+          <t>count [ncit]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>An assessment used to quantify and describe the colors within the visible spectrum of light.</t>
+          <t>Determining the number or amount of something.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
